--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1945,6 +1945,108 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129650574</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97604</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kavelberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>549937</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6698947</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97633</v>
+        <v>97645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97646</v>
+        <v>97651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97655</v>
+        <v>97657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97657</v>
+        <v>97667</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2047,6 +2047,122 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129661158</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lappkyrkan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>549729</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6698892</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129661158</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>129650574</v>
       </c>
       <c r="B14" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129661158</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -2052,7 +2052,7 @@
         <v>129661158</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -2052,7 +2052,7 @@
         <v>129661158</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34602-2025 artfynd.xlsx
+++ b/artfynd/A 34602-2025 artfynd.xlsx
@@ -2052,7 +2052,7 @@
         <v>129661158</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
